--- a/StateOfPractice/DomainMeasurements/InverseKinematics-Ryan/Software_List.xlsx
+++ b/StateOfPractice/DomainMeasurements/InverseKinematics-Ryan/Software_List.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\course\ResearchProject\AIMSS\StateOfPractice\DomainMeasurements\InverseKinematics-Ryan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8289F5DD-A9DB-4D66-B3F9-0F2B0D0D43E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1009004-DF67-4B71-B3CF-ACCF719B899C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="810" yWindow="-120" windowWidth="28110" windowHeight="16440" xr2:uid="{2279FB42-8099-4FD6-9EF2-F606B56203F5}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="simulator and motion planning" sheetId="2" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="144">
   <si>
     <t>Software / Library</t>
   </si>
@@ -510,12 +511,423 @@
     <t>https://moveit.picknik.ai/main/doc/examples/ikfast/ikfast_tutorial.htmlhttps://github.com/rdiankov/openrave/tree/master/plugins/ikfastsolvers</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>GitHub Topic: motion-planning</t>
+  </si>
+  <si>
+    <t>https://github.com/topics/motion-planning</t>
+  </si>
+  <si>
+    <t>GitHub Topic: robotics-simulation</t>
+  </si>
+  <si>
+    <t>https://github.com/topics/robotics-simulation</t>
+  </si>
+  <si>
+    <t>Awesome Robotics Libraries</t>
+  </si>
+  <si>
+    <t>https://github.com/jslee02/awesome-robotics-libraries</t>
+  </si>
+  <si>
+    <t>Awesome Robotics（ahundt）</t>
+  </si>
+  <si>
+    <t>https://github.com/ahundt/awesome-robotics</t>
+  </si>
+  <si>
+    <t>Awesome Robotics（kiloreux）</t>
+  </si>
+  <si>
+    <t>https://github.com/kiloreux/awesome-robotics</t>
+  </si>
+  <si>
+    <t>Awesome Motion Planning</t>
+  </si>
+  <si>
+    <t>https://github.com/AGV-IIT-KGP/awesome-motion-planning</t>
+  </si>
+  <si>
+    <t>Awesome Multibody Dynamics Simulation</t>
+  </si>
+  <si>
+    <t>https://github.com/jslee02/awesome-multibody-dynamics-simulation</t>
+  </si>
+  <si>
+    <t>Awesome Robotic Tooling</t>
+  </si>
+  <si>
+    <t>https://github.com/Ly0n/awesome-robotic-tooling</t>
+  </si>
+  <si>
+    <t>Awesome ROS 2</t>
+  </si>
+  <si>
+    <t>https://github.com/fkromer/awesome-ros2</t>
+  </si>
+  <si>
+    <t>Awesome Webots</t>
+  </si>
+  <si>
+    <t>https://github.com/lukicdarkoo/awesome-webots</t>
+  </si>
+  <si>
+    <t>Awesome Robotics Projects</t>
+  </si>
+  <si>
+    <t>https://github.com/mjyc/awesome-robotics-projects</t>
+  </si>
+  <si>
+    <t>https://en.wikipedia.org/wiki/Robotics_simulator</t>
+  </si>
+  <si>
+    <t>GitHub Topic: path-planning</t>
+  </si>
+  <si>
+    <t>https://github.com/topics/path-planning</t>
+  </si>
+  <si>
+    <t>GitHub Topic: robotics-navigation</t>
+  </si>
+  <si>
+    <t>https://github.com/topics/robotics-navigation</t>
+  </si>
+  <si>
+    <t>best-of-robot-simulators</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://github.com/knmcguire/best-of-robot-simulators</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wikipedia: Robotics simulator</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A Comparison of Humanoid Robot Simulators: A Quantitative Approach</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/abs/2008.04627</t>
+  </si>
+  <si>
+    <t>Gazebo、Webots、V-REP/CoppeliaSim</t>
+  </si>
+  <si>
+    <t>A Study on the Challenges of Using Robotics Simulators for Testing</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/abs/2004.07368</t>
+  </si>
+  <si>
+    <r>
+      <t>Gazebo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>Webots</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>MuJoCo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>PyBullet</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>GitHub Topic Page (community aggregation)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> – Browse active and popular motion planning projects.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>GitHub Topic Page</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> – Aggregates projects related to robotic simulators.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>GitHub Topic Page</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> – Aggregates projects related to robotic simulation ecosystems.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Community-recognized robotics library list</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, containing sections such as “Motion Planning” and “Simulation.”</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Comprehensive Awesome Robotics list</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, including categories on planning, optimization, and simulation resources.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Community-maintained comprehensive robotics list</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, containing sections for planning and simulation.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Curated list for motion planning</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, covering both classical and modern libraries, papers, and implementations.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Curated list for multibody dynamics and simulation</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, covering mainstream simulators and physics engines.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Curated list of robotic tools and libraries</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, including IK, kinematics, visualization, and simulation tools.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Curated list for the ROS 2 ecosystem</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, including navigation, planning, and simulation integrations.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Curated list for the Webots ecosystem</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, aggregating examples, interfaces, and tutorials.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Curated list of robotics projects</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, including projects involving planning and simulation components.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Wikipedia article “Robotics simulator”</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, aggregating related links and resources.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>GitHub Topic Page</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> – Aggregates projects related to path or motion planning.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>GitHub Topic Page</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> – Aggregates projects related to navigation and planning.</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -573,21 +985,69 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF333333"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF333333"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF333333"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFD6D6D6"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFD6D6D6"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFD6D6D6"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFD6D6D6"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -599,7 +1059,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -622,6 +1082,21 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -938,6 +1413,395 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{470785A9-3101-4DC5-BBE3-8DD6D2B3E6BB}">
+  <dimension ref="A1:E45"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="98.75" customWidth="1"/>
+    <col min="2" max="2" width="73.25" customWidth="1"/>
+    <col min="3" max="3" width="39.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="8"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+    </row>
+    <row r="2" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="29.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="29.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="29.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="29.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="29.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="29.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="29.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="29.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="29.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="29.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>141</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="29.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="19" spans="1:5" ht="121.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="D19" s="11"/>
+      <c r="E19" s="9" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="138.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="B20" s="9">
+        <v>2020</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="D20" s="9"/>
+      <c r="E20" s="9" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="9"/>
+      <c r="B21" s="9"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="11"/>
+    </row>
+    <row r="22" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="9"/>
+      <c r="B22" s="9"/>
+      <c r="C22" s="10"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="9"/>
+    </row>
+    <row r="23" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="9"/>
+      <c r="B23" s="9"/>
+      <c r="C23" s="10"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="9"/>
+    </row>
+    <row r="24" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="9"/>
+      <c r="B24" s="9"/>
+      <c r="C24" s="10"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="9"/>
+    </row>
+    <row r="25" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="9"/>
+      <c r="B25" s="9"/>
+      <c r="C25" s="10"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="9"/>
+    </row>
+    <row r="26" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="9"/>
+      <c r="B26" s="9"/>
+      <c r="C26" s="10"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="9"/>
+    </row>
+    <row r="27" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="9"/>
+      <c r="C27" s="10"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="9"/>
+    </row>
+    <row r="28" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="9"/>
+      <c r="C28" s="10"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="9"/>
+    </row>
+    <row r="29" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="9"/>
+      <c r="C29" s="10"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="9"/>
+    </row>
+    <row r="30" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="9"/>
+      <c r="C30" s="10"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="9"/>
+    </row>
+    <row r="31" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="9"/>
+      <c r="C31" s="10"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="9"/>
+    </row>
+    <row r="32" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="9"/>
+      <c r="C32" s="10"/>
+      <c r="D32" s="9"/>
+      <c r="E32" s="9"/>
+    </row>
+    <row r="33" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="9"/>
+      <c r="C33" s="10"/>
+      <c r="D33" s="9"/>
+      <c r="E33" s="9"/>
+    </row>
+    <row r="34" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="9"/>
+      <c r="C34" s="10"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="9"/>
+    </row>
+    <row r="35" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="9"/>
+      <c r="C35" s="10"/>
+      <c r="D35" s="9"/>
+      <c r="E35" s="9"/>
+    </row>
+    <row r="36" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="9"/>
+      <c r="C36" s="10"/>
+      <c r="D36" s="9"/>
+      <c r="E36" s="9"/>
+    </row>
+    <row r="37" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="9"/>
+      <c r="C37" s="10"/>
+      <c r="D37" s="9"/>
+      <c r="E37" s="9"/>
+    </row>
+    <row r="38" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="9"/>
+      <c r="C38" s="10"/>
+      <c r="D38" s="9"/>
+      <c r="E38" s="9"/>
+    </row>
+    <row r="39" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="9"/>
+      <c r="C39" s="10"/>
+      <c r="D39" s="9"/>
+      <c r="E39" s="9"/>
+    </row>
+    <row r="40" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="9"/>
+      <c r="C40" s="10"/>
+      <c r="D40" s="9"/>
+      <c r="E40" s="9"/>
+    </row>
+    <row r="41" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="9"/>
+      <c r="C41" s="10"/>
+      <c r="D41" s="9"/>
+      <c r="E41" s="9"/>
+    </row>
+    <row r="42" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="9"/>
+      <c r="C42" s="10"/>
+      <c r="D42" s="9"/>
+      <c r="E42" s="9"/>
+    </row>
+    <row r="43" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="9"/>
+      <c r="C43" s="10"/>
+      <c r="D43" s="9"/>
+      <c r="E43" s="9"/>
+    </row>
+    <row r="44" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="9"/>
+      <c r="C44" s="10"/>
+      <c r="D44" s="9"/>
+      <c r="E44" s="9"/>
+    </row>
+    <row r="45" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="9"/>
+      <c r="C45" s="10"/>
+      <c r="D45" s="9"/>
+      <c r="E45" s="9"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{0F86DE13-1A53-42F1-A468-2240B965FF87}"/>
+    <hyperlink ref="C3" r:id="rId2" xr:uid="{6751552D-430F-4455-BDD6-BEFAD682B04F}"/>
+    <hyperlink ref="C4" r:id="rId3" xr:uid="{B6960A22-4234-43F2-B87B-D0AD9FB0194E}"/>
+    <hyperlink ref="C5" r:id="rId4" xr:uid="{7460CFCE-E28D-43C3-9EF8-F94BA9D47F09}"/>
+    <hyperlink ref="C6" r:id="rId5" xr:uid="{784A2DAC-0EAD-4A05-B7FE-87FC58AA4945}"/>
+    <hyperlink ref="C7" r:id="rId6" xr:uid="{40C54A23-4AC4-4107-8EE6-7D82C3A5665D}"/>
+    <hyperlink ref="C8" r:id="rId7" xr:uid="{53A7F545-0A82-4B46-B88D-204594E5E295}"/>
+    <hyperlink ref="C9" r:id="rId8" xr:uid="{F0DC4D60-E333-40AA-AB47-EEB077472AE5}"/>
+    <hyperlink ref="C10" r:id="rId9" xr:uid="{661CF3D0-D067-4A31-8F4B-3D2C8930DF59}"/>
+    <hyperlink ref="C11" r:id="rId10" xr:uid="{E5E0948F-81EE-47FE-BF27-92487AA850E2}"/>
+    <hyperlink ref="C12" r:id="rId11" xr:uid="{B4F29626-3EA9-4342-BBC3-D5B6F38F109A}"/>
+    <hyperlink ref="C13" r:id="rId12" xr:uid="{AB762E82-E2DB-43B2-A252-BAE236100474}"/>
+    <hyperlink ref="C14" r:id="rId13" xr:uid="{C1E40DA1-BB9A-43BA-9561-77364C51B762}"/>
+    <hyperlink ref="C15" r:id="rId14" xr:uid="{1B505C44-B907-4B4A-A348-6D6496A8D4B5}"/>
+    <hyperlink ref="C16" r:id="rId15" xr:uid="{50033A1F-5E24-40B6-BF84-1050FA82247D}"/>
+    <hyperlink ref="C19" r:id="rId16" xr:uid="{3BA11F5A-917D-4E52-9AC3-2CE7AB925C9C}"/>
+    <hyperlink ref="C20" r:id="rId17" xr:uid="{46B6CFBA-B0FC-4292-A3D8-20427C99F8FA}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{354D475D-67CE-47C1-879A-864A87C4D259}">
   <dimension ref="A1:D31"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
